--- a/artfynd/A 58498-2024 artfynd.xlsx
+++ b/artfynd/A 58498-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126494095</v>
+        <v>126493965</v>
       </c>
       <c r="B2" t="n">
-        <v>78386</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589549</v>
+        <v>589531</v>
       </c>
       <c r="R2" t="n">
-        <v>7293161</v>
+        <v>7293125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -783,7 +783,7 @@
         <v>126494100</v>
       </c>
       <c r="B3" t="n">
-        <v>79004</v>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126493965</v>
+        <v>126494095</v>
       </c>
       <c r="B4" t="n">
-        <v>91241</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589531</v>
+        <v>589549</v>
       </c>
       <c r="R4" t="n">
-        <v>7293125</v>
+        <v>7293161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126493938</v>
+        <v>126493931</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589519</v>
+        <v>589498</v>
       </c>
       <c r="R5" t="n">
-        <v>7293101</v>
+        <v>7293083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
         <v>126493978</v>
       </c>
       <c r="B6" t="n">
-        <v>77929</v>
+        <v>78334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126493931</v>
+        <v>126494091</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>78334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589498</v>
+        <v>589549</v>
       </c>
       <c r="R7" t="n">
-        <v>7293083</v>
+        <v>7293161</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,111 +1302,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126494091</v>
-      </c>
-      <c r="B8" t="n">
-        <v>77929</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6487</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Blågrå svartspik</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis fennica</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Holmträsket/Skansnäs Abborrtjärnen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>589549</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7293161</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Luckig, lågproduktiv och lövrik grannaturskog med inslag av torrakor av tall</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58498-2024 artfynd.xlsx
+++ b/artfynd/A 58498-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494100</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493931</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,8 +1332,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126494091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>